--- a/research/traditional_assets/database/data/spain/spain_investments_asset_management.xlsx
+++ b/research/traditional_assets/database/data/spain/spain_investments_asset_management.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ5"/>
+  <dimension ref="A1:AQ6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -587,116 +587,119 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
+      <c r="D2">
+        <v>0.385</v>
+      </c>
       <c r="G2">
-        <v>0.4026451226810293</v>
+        <v>0.4427431610942248</v>
       </c>
       <c r="H2">
-        <v>0.4026211849192101</v>
+        <v>0.4427431610942248</v>
       </c>
       <c r="I2">
-        <v>0.577510472770796</v>
+        <v>0.3667553191489362</v>
       </c>
       <c r="J2">
-        <v>0.4812587273089967</v>
+        <v>0.3307898354108461</v>
       </c>
       <c r="K2">
-        <v>4.361</v>
+        <v>4.055</v>
       </c>
       <c r="L2">
-        <v>0.05219628964691801</v>
+        <v>0.1540653495440729</v>
       </c>
       <c r="M2">
-        <v>12.3542</v>
+        <v>7.761</v>
       </c>
       <c r="N2">
-        <v>0.01511956920817525</v>
+        <v>0.03870822942643391</v>
       </c>
       <c r="O2">
-        <v>2.832882366429718</v>
+        <v>1.913933415536375</v>
       </c>
       <c r="P2">
-        <v>12.1122</v>
+        <v>5.285</v>
       </c>
       <c r="Q2">
-        <v>0.01482339982866234</v>
+        <v>0.02635910224438903</v>
       </c>
       <c r="R2">
-        <v>2.777390506764504</v>
+        <v>1.303329223181258</v>
       </c>
       <c r="S2">
-        <v>0.242</v>
+        <v>2.476</v>
       </c>
       <c r="T2">
-        <v>0.01958848003108254</v>
+        <v>0.3190310526993944</v>
       </c>
       <c r="U2">
-        <v>71.43000000000001</v>
+        <v>13.393</v>
       </c>
       <c r="V2">
-        <v>0.08741892057275732</v>
+        <v>0.06679800498753118</v>
       </c>
       <c r="W2">
-        <v>-0.002090032154340836</v>
+        <v>0.04680952380952381</v>
       </c>
       <c r="X2">
-        <v>0.06733441407282867</v>
+        <v>0.1014161161799283</v>
       </c>
       <c r="Y2">
-        <v>-0.06942444622716951</v>
+        <v>-0.05460659237040446</v>
       </c>
       <c r="Z2">
-        <v>0.0660808630453352</v>
+        <v>0.1385824781622026</v>
       </c>
       <c r="AA2">
-        <v>0.007346241457858769</v>
+        <v>0.02654455992739641</v>
       </c>
       <c r="AB2">
-        <v>0.0576165930053808</v>
+        <v>0.09015035143447128</v>
       </c>
       <c r="AC2">
-        <v>-0.05027035154752203</v>
+        <v>-0.06523684007289669</v>
       </c>
       <c r="AD2">
-        <v>596.6</v>
+        <v>116.01</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>596.6</v>
+        <v>116.01</v>
       </c>
       <c r="AG2">
-        <v>525.1700000000001</v>
+        <v>102.617</v>
       </c>
       <c r="AH2">
-        <v>0.4220131569639952</v>
+        <v>0.3665287036744495</v>
       </c>
       <c r="AI2">
-        <v>0.4552808302808303</v>
+        <v>0.5076801890508075</v>
       </c>
       <c r="AJ2">
-        <v>0.3912551126077466</v>
+        <v>0.3385392439223138</v>
       </c>
       <c r="AK2">
-        <v>0.423876284332954</v>
+        <v>0.4770287796873329</v>
       </c>
       <c r="AL2">
-        <v>16.825</v>
+        <v>3.2</v>
       </c>
       <c r="AM2">
-        <v>16.757</v>
+        <v>3.075</v>
       </c>
       <c r="AN2">
-        <v>11.9243684042213</v>
+        <v>10.40168564511791</v>
       </c>
       <c r="AO2">
-        <v>2.867815750371471</v>
+        <v>3.0165625</v>
       </c>
       <c r="AP2">
-        <v>10.496682123441</v>
+        <v>9.200842822558954</v>
       </c>
       <c r="AQ2">
-        <v>2.879453362773767</v>
+        <v>3.139186991869919</v>
       </c>
     </row>
     <row r="3">
@@ -707,7 +710,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Castellana Properties Socimi, S.A. (BME:YCPS)</t>
+          <t>Axon Partners Group, S.A. (BME:APG)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -716,115 +719,100 @@
         </is>
       </c>
       <c r="G3">
-        <v>0.3849009900990099</v>
+        <v>0.2662337662337662</v>
       </c>
       <c r="H3">
-        <v>0.3849009900990099</v>
+        <v>0.2662337662337662</v>
       </c>
       <c r="I3">
-        <v>0.582920792079208</v>
+        <v>0.2603896103896104</v>
       </c>
       <c r="J3">
-        <v>0.582920792079208</v>
+        <v>0.1775383707201889</v>
       </c>
       <c r="K3">
-        <v>4.62</v>
+        <v>4.6</v>
       </c>
       <c r="L3">
-        <v>0.05717821782178218</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="M3">
-        <v>7.041200000000001</v>
+        <v>3.14</v>
       </c>
       <c r="N3">
-        <v>0.01051867343890051</v>
+        <v>0.02883379247015611</v>
       </c>
       <c r="O3">
-        <v>1.524069264069264</v>
+        <v>0.682608695652174</v>
       </c>
       <c r="P3">
-        <v>6.982200000000001</v>
+        <v>3.14</v>
       </c>
       <c r="Q3">
-        <v>0.01043053480729011</v>
+        <v>0.02883379247015611</v>
       </c>
       <c r="R3">
-        <v>1.511298701298701</v>
+        <v>0.682608695652174</v>
       </c>
       <c r="S3">
-        <v>0.05900000000000016</v>
+        <v>0</v>
       </c>
       <c r="T3">
-        <v>0.008379253536329057</v>
+        <v>0</v>
       </c>
       <c r="U3">
-        <v>61.1</v>
+        <v>4.15</v>
       </c>
       <c r="V3">
-        <v>0.09127576934568271</v>
-      </c>
-      <c r="W3">
-        <v>0.007619990103908957</v>
+        <v>0.03810835629017447</v>
       </c>
       <c r="X3">
-        <v>0.08036250568882317</v>
-      </c>
-      <c r="Y3">
-        <v>-0.07274251558491421</v>
-      </c>
-      <c r="Z3">
-        <v>0.07168840386833467</v>
-      </c>
-      <c r="AA3">
-        <v>0.0417886611658238</v>
+        <v>0.0885746918450192</v>
       </c>
       <c r="AB3">
-        <v>0.059015537125604</v>
-      </c>
-      <c r="AC3">
-        <v>-0.0172268759597802</v>
+        <v>0.08823912015812756</v>
       </c>
       <c r="AD3">
-        <v>558.9</v>
+        <v>1.24</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>558.9</v>
+        <v>1.24</v>
       </c>
       <c r="AG3">
-        <v>497.8</v>
+        <v>-2.91</v>
       </c>
       <c r="AH3">
-        <v>0.4550191321338435</v>
+        <v>0.01125839840203378</v>
       </c>
       <c r="AI3">
-        <v>0.4829344163138339</v>
+        <v>0.09295352323838081</v>
       </c>
       <c r="AJ3">
-        <v>0.4264907470870459</v>
+        <v>-0.02745542032267195</v>
       </c>
       <c r="AK3">
-        <v>0.4541142127349024</v>
+        <v>-0.3166485310119695</v>
       </c>
       <c r="AL3">
-        <v>15.3</v>
+        <v>0.062</v>
       </c>
       <c r="AM3">
-        <v>15.3</v>
+        <v>0.062</v>
       </c>
       <c r="AN3">
-        <v>11.84110169491525</v>
+        <v>0.3212435233160622</v>
       </c>
       <c r="AO3">
-        <v>3.07843137254902</v>
+        <v>64.6774193548387</v>
       </c>
       <c r="AP3">
-        <v>10.54661016949152</v>
+        <v>-0.7538860103626943</v>
       </c>
       <c r="AQ3">
-        <v>3.07843137254902</v>
+        <v>64.6774193548387</v>
       </c>
     </row>
     <row r="4">
@@ -835,7 +823,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Elaia Investment Spain Socimi, S.A. (BME:YEIS)</t>
+          <t>JSS Real Estate SOCIMI, S.A. (BME:YJSS)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -844,115 +832,115 @@
         </is>
       </c>
       <c r="G4">
-        <v>0.968</v>
+        <v>0.8252873563218391</v>
       </c>
       <c r="H4">
-        <v>0.9672727272727273</v>
+        <v>0.8252873563218391</v>
       </c>
       <c r="I4">
-        <v>0.4690909090909091</v>
+        <v>0.6471264367816092</v>
       </c>
       <c r="J4">
-        <v>0.2345454545454546</v>
+        <v>0.6471264367816092</v>
       </c>
       <c r="K4">
-        <v>-0.13</v>
+        <v>2.8</v>
       </c>
       <c r="L4">
-        <v>-0.04727272727272727</v>
+        <v>0.3218390804597701</v>
       </c>
       <c r="M4">
-        <v>5.313</v>
+        <v>1.81</v>
       </c>
       <c r="N4">
-        <v>0.06156431054461182</v>
+        <v>0.03278985507246377</v>
       </c>
       <c r="O4">
-        <v>-40.86923076923077</v>
+        <v>0.6464285714285715</v>
       </c>
       <c r="P4">
-        <v>5.13</v>
+        <v>1.81</v>
       </c>
       <c r="Q4">
-        <v>0.05944380069524913</v>
+        <v>0.03278985507246377</v>
       </c>
       <c r="R4">
-        <v>-39.46153846153846</v>
+        <v>0.6464285714285715</v>
       </c>
       <c r="S4">
-        <v>0.1829999999999998</v>
+        <v>0</v>
       </c>
       <c r="T4">
-        <v>0.03444381705251268</v>
+        <v>0</v>
       </c>
       <c r="U4">
-        <v>6.55</v>
+        <v>7.47</v>
       </c>
       <c r="V4">
-        <v>0.07589803012746234</v>
+        <v>0.1353260869565217</v>
       </c>
       <c r="W4">
-        <v>-0.002090032154340836</v>
+        <v>0.04761904761904762</v>
       </c>
       <c r="X4">
-        <v>0.06733441407282867</v>
+        <v>0.1570197329866702</v>
       </c>
       <c r="Y4">
-        <v>-0.06942444622716951</v>
+        <v>-0.1094006853676226</v>
       </c>
       <c r="Z4">
-        <v>0.03132118451025057</v>
+        <v>0.05256797583081572</v>
       </c>
       <c r="AA4">
-        <v>0.007346241457858769</v>
+        <v>0.03401812688821753</v>
       </c>
       <c r="AB4">
-        <v>0.0576165930053808</v>
+        <v>0.09311588767912551</v>
       </c>
       <c r="AC4">
-        <v>-0.05027035154752203</v>
+        <v>-0.05909776079090798</v>
       </c>
       <c r="AD4">
-        <v>34.7</v>
+        <v>102.7</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>34.7</v>
+        <v>102.7</v>
       </c>
       <c r="AG4">
-        <v>28.15</v>
+        <v>95.23</v>
       </c>
       <c r="AH4">
-        <v>0.2867768595041322</v>
+        <v>0.6504116529449019</v>
       </c>
       <c r="AI4">
-        <v>0.3656480505795575</v>
+        <v>0.6414740787008121</v>
       </c>
       <c r="AJ4">
-        <v>0.2459589340323285</v>
+        <v>0.6330519178355382</v>
       </c>
       <c r="AK4">
-        <v>0.3186191284663271</v>
+        <v>0.6239271440739043</v>
       </c>
       <c r="AL4">
-        <v>1.41</v>
+        <v>2.83</v>
       </c>
       <c r="AM4">
-        <v>1.41</v>
+        <v>2.83</v>
       </c>
       <c r="AN4">
-        <v>11.68350168350168</v>
+        <v>14.30362116991644</v>
       </c>
       <c r="AO4">
-        <v>0.9148936170212767</v>
+        <v>1.989399293286219</v>
       </c>
       <c r="AP4">
-        <v>9.478114478114477</v>
+        <v>13.26323119777159</v>
       </c>
       <c r="AQ4">
-        <v>0.9148936170212767</v>
+        <v>1.989399293286219</v>
       </c>
     </row>
     <row r="5">
@@ -963,7 +951,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Inbest Prime I Inmuebles SOCIMI, S.A. (BME:YINB1)</t>
+          <t>Quid Pro Quo Alquiler Seguro SOCIMI, S.A (BME:YQPQ)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -971,98 +959,247 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
+      <c r="G5">
+        <v>0.3972477064220183</v>
+      </c>
+      <c r="H5">
+        <v>0.3972477064220183</v>
+      </c>
+      <c r="I5">
+        <v>0.3293577981651376</v>
+      </c>
+      <c r="J5">
+        <v>0.3049609242269793</v>
+      </c>
       <c r="K5">
-        <v>-0.129</v>
+        <v>0.575</v>
+      </c>
+      <c r="L5">
+        <v>0.5275229357798165</v>
       </c>
       <c r="M5">
-        <v>-0</v>
+        <v>0.411</v>
       </c>
       <c r="N5">
-        <v>-0</v>
+        <v>0.03605263157894737</v>
       </c>
       <c r="O5">
-        <v>0</v>
+        <v>0.7147826086956522</v>
       </c>
       <c r="P5">
-        <v>-0</v>
+        <v>0.335</v>
       </c>
       <c r="Q5">
-        <v>-0</v>
+        <v>0.0293859649122807</v>
       </c>
       <c r="R5">
-        <v>0</v>
+        <v>0.582608695652174</v>
       </c>
       <c r="S5">
-        <v>0</v>
+        <v>0.07600000000000001</v>
+      </c>
+      <c r="T5">
+        <v>0.1849148418491484</v>
       </c>
       <c r="U5">
-        <v>3.78</v>
+        <v>0.899</v>
       </c>
       <c r="V5">
-        <v>0.06156351791530944</v>
+        <v>0.07885964912280702</v>
       </c>
       <c r="W5">
-        <v>-0.002733050847457627</v>
+        <v>0.046</v>
       </c>
       <c r="X5">
-        <v>0.05670266318434938</v>
+        <v>0.104063137068678</v>
       </c>
       <c r="Y5">
-        <v>-0.059435714031807</v>
+        <v>-0.05806313706867798</v>
       </c>
       <c r="Z5">
-        <v>0</v>
+        <v>0.06253585771658061</v>
       </c>
       <c r="AA5">
-        <v>-0.002810351799433886</v>
+        <v>0.01907099296657529</v>
       </c>
       <c r="AB5">
-        <v>0.0556193744002761</v>
+        <v>0.09044691232146071</v>
       </c>
       <c r="AC5">
-        <v>-0.05842972619970999</v>
+        <v>-0.07137591935488541</v>
       </c>
       <c r="AD5">
-        <v>3</v>
+        <v>4.9</v>
       </c>
       <c r="AE5">
         <v>0</v>
       </c>
       <c r="AF5">
-        <v>3</v>
+        <v>4.9</v>
       </c>
       <c r="AG5">
-        <v>-0.7799999999999998</v>
+        <v>4.001</v>
       </c>
       <c r="AH5">
-        <v>0.04658385093167702</v>
+        <v>0.3006134969325153</v>
       </c>
       <c r="AI5">
-        <v>0.05154639175257732</v>
+        <v>0.3024691358024691</v>
       </c>
       <c r="AJ5">
-        <v>-0.01286704058066644</v>
+        <v>0.2597883254334135</v>
       </c>
       <c r="AK5">
-        <v>-0.01433296582138919</v>
+        <v>0.2614861773740279</v>
       </c>
       <c r="AL5">
-        <v>0.115</v>
+        <v>0.091</v>
       </c>
       <c r="AM5">
-        <v>0.047</v>
+        <v>0.091</v>
       </c>
       <c r="AN5">
-        <v>-21.73913043478261</v>
+        <v>11.86440677966102</v>
       </c>
       <c r="AO5">
-        <v>-1.208695652173913</v>
+        <v>3.945054945054945</v>
       </c>
       <c r="AP5">
-        <v>5.652173913043477</v>
+        <v>9.687651331719129</v>
       </c>
       <c r="AQ5">
-        <v>-2.957446808510638</v>
+        <v>3.945054945054945</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Spain</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Iffe Futura, S.A. (BME:IFF)</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Investments &amp; Asset Management</t>
+        </is>
+      </c>
+      <c r="D6">
+        <v>0.385</v>
+      </c>
+      <c r="G6">
+        <v>-0.05309734513274337</v>
+      </c>
+      <c r="H6">
+        <v>-0.05309734513274337</v>
+      </c>
+      <c r="I6">
+        <v>-0.3061946902654867</v>
+      </c>
+      <c r="J6">
+        <v>-0.3061946902654867</v>
+      </c>
+      <c r="K6">
+        <v>-3.92</v>
+      </c>
+      <c r="L6">
+        <v>-3.469026548672566</v>
+      </c>
+      <c r="M6">
+        <v>2.4</v>
+      </c>
+      <c r="N6">
+        <v>0.096</v>
+      </c>
+      <c r="O6">
+        <v>-0.6122448979591837</v>
+      </c>
+      <c r="P6">
+        <v>-0</v>
+      </c>
+      <c r="Q6">
+        <v>-0</v>
+      </c>
+      <c r="R6">
+        <v>0</v>
+      </c>
+      <c r="S6">
+        <v>2.4</v>
+      </c>
+      <c r="T6">
+        <v>1</v>
+      </c>
+      <c r="U6">
+        <v>0.874</v>
+      </c>
+      <c r="V6">
+        <v>0.03496</v>
+      </c>
+      <c r="W6">
+        <v>-0.09116279069767441</v>
+      </c>
+      <c r="X6">
+        <v>0.09876909529117857</v>
+      </c>
+      <c r="Y6">
+        <v>-0.189931885988853</v>
+      </c>
+      <c r="Z6">
+        <v>0.1615901615901617</v>
+      </c>
+      <c r="AA6">
+        <v>-0.04947804947804951</v>
+      </c>
+      <c r="AB6">
+        <v>0.08985379054748187</v>
+      </c>
+      <c r="AC6">
+        <v>-0.1393318400255314</v>
+      </c>
+      <c r="AD6">
+        <v>7.17</v>
+      </c>
+      <c r="AE6">
+        <v>0</v>
+      </c>
+      <c r="AF6">
+        <v>7.17</v>
+      </c>
+      <c r="AG6">
+        <v>6.296</v>
+      </c>
+      <c r="AH6">
+        <v>0.222878458190861</v>
+      </c>
+      <c r="AI6">
+        <v>0.1844610239259069</v>
+      </c>
+      <c r="AJ6">
+        <v>0.2011758691206544</v>
+      </c>
+      <c r="AK6">
+        <v>0.1657016528055585</v>
+      </c>
+      <c r="AL6">
+        <v>0.217</v>
+      </c>
+      <c r="AM6">
+        <v>0.092</v>
+      </c>
+      <c r="AN6">
+        <v>-23.9</v>
+      </c>
+      <c r="AO6">
+        <v>-1.594470046082949</v>
+      </c>
+      <c r="AP6">
+        <v>-20.98666666666667</v>
+      </c>
+      <c r="AQ6">
+        <v>-3.760869565217391</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/spain/spain_investments_asset_management.xlsx
+++ b/research/traditional_assets/database/data/spain/spain_investments_asset_management.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ6"/>
+  <dimension ref="A1:AQ3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -587,119 +587,110 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
-      <c r="D2">
-        <v>0.385</v>
-      </c>
       <c r="G2">
-        <v>0.4427431610942248</v>
+        <v>0.6353383458646616</v>
       </c>
       <c r="H2">
-        <v>0.4427431610942248</v>
+        <v>0.6353383458646616</v>
       </c>
       <c r="I2">
-        <v>0.3667553191489362</v>
+        <v>0.6353383458646616</v>
       </c>
       <c r="J2">
-        <v>0.3307898354108461</v>
+        <v>0.6353383458646616</v>
       </c>
       <c r="K2">
-        <v>4.055</v>
+        <v>0.22</v>
       </c>
       <c r="L2">
-        <v>0.1540653495440729</v>
+        <v>0.8270676691729323</v>
       </c>
       <c r="M2">
-        <v>7.761</v>
+        <v>2.01</v>
       </c>
       <c r="N2">
-        <v>0.03870822942643391</v>
+        <v>0.08072289156626505</v>
       </c>
       <c r="O2">
-        <v>1.913933415536375</v>
+        <v>9.136363636363635</v>
       </c>
       <c r="P2">
-        <v>5.285</v>
+        <v>2.01</v>
       </c>
       <c r="Q2">
-        <v>0.02635910224438903</v>
+        <v>0.08072289156626505</v>
       </c>
       <c r="R2">
-        <v>1.303329223181258</v>
+        <v>9.136363636363635</v>
       </c>
       <c r="S2">
-        <v>2.476</v>
+        <v>0</v>
       </c>
       <c r="T2">
-        <v>0.3190310526993944</v>
+        <v>0</v>
       </c>
       <c r="U2">
-        <v>13.393</v>
+        <v>0.399</v>
       </c>
       <c r="V2">
-        <v>0.06679800498753118</v>
+        <v>0.01602409638554217</v>
       </c>
       <c r="W2">
-        <v>0.04680952380952381</v>
+        <v>0.007971014492753623</v>
       </c>
       <c r="X2">
-        <v>0.1014161161799283</v>
+        <v>0.07425542537476212</v>
       </c>
       <c r="Y2">
-        <v>-0.05460659237040446</v>
+        <v>-0.0662844108820085</v>
       </c>
       <c r="Z2">
-        <v>0.1385824781622026</v>
+        <v>0.009763976067246632</v>
       </c>
       <c r="AA2">
-        <v>0.02654455992739641</v>
+        <v>0.00620342840362662</v>
       </c>
       <c r="AB2">
-        <v>0.09015035143447128</v>
+        <v>0.07425542537476212</v>
       </c>
       <c r="AC2">
-        <v>-0.06523684007289669</v>
+        <v>-0.06805199697113551</v>
       </c>
       <c r="AD2">
-        <v>116.01</v>
+        <v>0</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>116.01</v>
+        <v>0</v>
       </c>
       <c r="AG2">
-        <v>102.617</v>
+        <v>-0.399</v>
       </c>
       <c r="AH2">
-        <v>0.3665287036744495</v>
+        <v>0</v>
       </c>
       <c r="AI2">
-        <v>0.5076801890508075</v>
+        <v>0</v>
       </c>
       <c r="AJ2">
-        <v>0.3385392439223138</v>
+        <v>-0.01628504958981266</v>
       </c>
       <c r="AK2">
-        <v>0.4770287796873329</v>
+        <v>-0.01676400151254149</v>
       </c>
       <c r="AL2">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AM2">
-        <v>3.075</v>
+        <v>0</v>
       </c>
       <c r="AN2">
-        <v>10.40168564511791</v>
-      </c>
-      <c r="AO2">
-        <v>3.0165625</v>
+        <v>0</v>
       </c>
       <c r="AP2">
-        <v>9.200842822558954</v>
-      </c>
-      <c r="AQ2">
-        <v>3.139186991869919</v>
+        <v>-2.36094674556213</v>
       </c>
     </row>
     <row r="3">
@@ -710,7 +701,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Axon Partners Group, S.A. (BME:APG)</t>
+          <t>Inbest Prime III Inmuebles SOCIMI, S.A. (BME:YINB3)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -719,40 +710,40 @@
         </is>
       </c>
       <c r="G3">
-        <v>0.2662337662337662</v>
+        <v>0.6353383458646616</v>
       </c>
       <c r="H3">
-        <v>0.2662337662337662</v>
+        <v>0.6353383458646616</v>
       </c>
       <c r="I3">
-        <v>0.2603896103896104</v>
+        <v>0.6353383458646616</v>
       </c>
       <c r="J3">
-        <v>0.1775383707201889</v>
+        <v>0.6353383458646616</v>
       </c>
       <c r="K3">
-        <v>4.6</v>
+        <v>0.22</v>
       </c>
       <c r="L3">
-        <v>0.2987012987012987</v>
+        <v>0.8270676691729323</v>
       </c>
       <c r="M3">
-        <v>3.14</v>
+        <v>2.01</v>
       </c>
       <c r="N3">
-        <v>0.02883379247015611</v>
+        <v>0.08072289156626505</v>
       </c>
       <c r="O3">
-        <v>0.682608695652174</v>
+        <v>9.136363636363635</v>
       </c>
       <c r="P3">
-        <v>3.14</v>
+        <v>2.01</v>
       </c>
       <c r="Q3">
-        <v>0.02883379247015611</v>
+        <v>0.08072289156626505</v>
       </c>
       <c r="R3">
-        <v>0.682608695652174</v>
+        <v>9.136363636363635</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -761,445 +752,67 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>4.15</v>
+        <v>0.399</v>
       </c>
       <c r="V3">
-        <v>0.03810835629017447</v>
+        <v>0.01602409638554217</v>
+      </c>
+      <c r="W3">
+        <v>0.007971014492753623</v>
       </c>
       <c r="X3">
-        <v>0.0885746918450192</v>
+        <v>0.07425542537476212</v>
+      </c>
+      <c r="Y3">
+        <v>-0.0662844108820085</v>
+      </c>
+      <c r="Z3">
+        <v>0.009763976067246632</v>
+      </c>
+      <c r="AA3">
+        <v>0.00620342840362662</v>
       </c>
       <c r="AB3">
-        <v>0.08823912015812756</v>
+        <v>0.07425542537476212</v>
+      </c>
+      <c r="AC3">
+        <v>-0.06805199697113551</v>
       </c>
       <c r="AD3">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AG3">
-        <v>-2.91</v>
+        <v>-0.399</v>
       </c>
       <c r="AH3">
-        <v>0.01125839840203378</v>
+        <v>0</v>
       </c>
       <c r="AI3">
-        <v>0.09295352323838081</v>
+        <v>0</v>
       </c>
       <c r="AJ3">
-        <v>-0.02745542032267195</v>
+        <v>-0.01628504958981266</v>
       </c>
       <c r="AK3">
-        <v>-0.3166485310119695</v>
+        <v>-0.01676400151254149</v>
       </c>
       <c r="AL3">
-        <v>0.062</v>
+        <v>0</v>
       </c>
       <c r="AM3">
-        <v>0.062</v>
+        <v>0</v>
       </c>
       <c r="AN3">
-        <v>0.3212435233160622</v>
-      </c>
-      <c r="AO3">
-        <v>64.6774193548387</v>
+        <v>0</v>
       </c>
       <c r="AP3">
-        <v>-0.7538860103626943</v>
-      </c>
-      <c r="AQ3">
-        <v>64.6774193548387</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Spain</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>JSS Real Estate SOCIMI, S.A. (BME:YJSS)</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Investments &amp; Asset Management</t>
-        </is>
-      </c>
-      <c r="G4">
-        <v>0.8252873563218391</v>
-      </c>
-      <c r="H4">
-        <v>0.8252873563218391</v>
-      </c>
-      <c r="I4">
-        <v>0.6471264367816092</v>
-      </c>
-      <c r="J4">
-        <v>0.6471264367816092</v>
-      </c>
-      <c r="K4">
-        <v>2.8</v>
-      </c>
-      <c r="L4">
-        <v>0.3218390804597701</v>
-      </c>
-      <c r="M4">
-        <v>1.81</v>
-      </c>
-      <c r="N4">
-        <v>0.03278985507246377</v>
-      </c>
-      <c r="O4">
-        <v>0.6464285714285715</v>
-      </c>
-      <c r="P4">
-        <v>1.81</v>
-      </c>
-      <c r="Q4">
-        <v>0.03278985507246377</v>
-      </c>
-      <c r="R4">
-        <v>0.6464285714285715</v>
-      </c>
-      <c r="S4">
-        <v>0</v>
-      </c>
-      <c r="T4">
-        <v>0</v>
-      </c>
-      <c r="U4">
-        <v>7.47</v>
-      </c>
-      <c r="V4">
-        <v>0.1353260869565217</v>
-      </c>
-      <c r="W4">
-        <v>0.04761904761904762</v>
-      </c>
-      <c r="X4">
-        <v>0.1570197329866702</v>
-      </c>
-      <c r="Y4">
-        <v>-0.1094006853676226</v>
-      </c>
-      <c r="Z4">
-        <v>0.05256797583081572</v>
-      </c>
-      <c r="AA4">
-        <v>0.03401812688821753</v>
-      </c>
-      <c r="AB4">
-        <v>0.09311588767912551</v>
-      </c>
-      <c r="AC4">
-        <v>-0.05909776079090798</v>
-      </c>
-      <c r="AD4">
-        <v>102.7</v>
-      </c>
-      <c r="AE4">
-        <v>0</v>
-      </c>
-      <c r="AF4">
-        <v>102.7</v>
-      </c>
-      <c r="AG4">
-        <v>95.23</v>
-      </c>
-      <c r="AH4">
-        <v>0.6504116529449019</v>
-      </c>
-      <c r="AI4">
-        <v>0.6414740787008121</v>
-      </c>
-      <c r="AJ4">
-        <v>0.6330519178355382</v>
-      </c>
-      <c r="AK4">
-        <v>0.6239271440739043</v>
-      </c>
-      <c r="AL4">
-        <v>2.83</v>
-      </c>
-      <c r="AM4">
-        <v>2.83</v>
-      </c>
-      <c r="AN4">
-        <v>14.30362116991644</v>
-      </c>
-      <c r="AO4">
-        <v>1.989399293286219</v>
-      </c>
-      <c r="AP4">
-        <v>13.26323119777159</v>
-      </c>
-      <c r="AQ4">
-        <v>1.989399293286219</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Spain</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Quid Pro Quo Alquiler Seguro SOCIMI, S.A (BME:YQPQ)</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Investments &amp; Asset Management</t>
-        </is>
-      </c>
-      <c r="G5">
-        <v>0.3972477064220183</v>
-      </c>
-      <c r="H5">
-        <v>0.3972477064220183</v>
-      </c>
-      <c r="I5">
-        <v>0.3293577981651376</v>
-      </c>
-      <c r="J5">
-        <v>0.3049609242269793</v>
-      </c>
-      <c r="K5">
-        <v>0.575</v>
-      </c>
-      <c r="L5">
-        <v>0.5275229357798165</v>
-      </c>
-      <c r="M5">
-        <v>0.411</v>
-      </c>
-      <c r="N5">
-        <v>0.03605263157894737</v>
-      </c>
-      <c r="O5">
-        <v>0.7147826086956522</v>
-      </c>
-      <c r="P5">
-        <v>0.335</v>
-      </c>
-      <c r="Q5">
-        <v>0.0293859649122807</v>
-      </c>
-      <c r="R5">
-        <v>0.582608695652174</v>
-      </c>
-      <c r="S5">
-        <v>0.07600000000000001</v>
-      </c>
-      <c r="T5">
-        <v>0.1849148418491484</v>
-      </c>
-      <c r="U5">
-        <v>0.899</v>
-      </c>
-      <c r="V5">
-        <v>0.07885964912280702</v>
-      </c>
-      <c r="W5">
-        <v>0.046</v>
-      </c>
-      <c r="X5">
-        <v>0.104063137068678</v>
-      </c>
-      <c r="Y5">
-        <v>-0.05806313706867798</v>
-      </c>
-      <c r="Z5">
-        <v>0.06253585771658061</v>
-      </c>
-      <c r="AA5">
-        <v>0.01907099296657529</v>
-      </c>
-      <c r="AB5">
-        <v>0.09044691232146071</v>
-      </c>
-      <c r="AC5">
-        <v>-0.07137591935488541</v>
-      </c>
-      <c r="AD5">
-        <v>4.9</v>
-      </c>
-      <c r="AE5">
-        <v>0</v>
-      </c>
-      <c r="AF5">
-        <v>4.9</v>
-      </c>
-      <c r="AG5">
-        <v>4.001</v>
-      </c>
-      <c r="AH5">
-        <v>0.3006134969325153</v>
-      </c>
-      <c r="AI5">
-        <v>0.3024691358024691</v>
-      </c>
-      <c r="AJ5">
-        <v>0.2597883254334135</v>
-      </c>
-      <c r="AK5">
-        <v>0.2614861773740279</v>
-      </c>
-      <c r="AL5">
-        <v>0.091</v>
-      </c>
-      <c r="AM5">
-        <v>0.091</v>
-      </c>
-      <c r="AN5">
-        <v>11.86440677966102</v>
-      </c>
-      <c r="AO5">
-        <v>3.945054945054945</v>
-      </c>
-      <c r="AP5">
-        <v>9.687651331719129</v>
-      </c>
-      <c r="AQ5">
-        <v>3.945054945054945</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Spain</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Iffe Futura, S.A. (BME:IFF)</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Investments &amp; Asset Management</t>
-        </is>
-      </c>
-      <c r="D6">
-        <v>0.385</v>
-      </c>
-      <c r="G6">
-        <v>-0.05309734513274337</v>
-      </c>
-      <c r="H6">
-        <v>-0.05309734513274337</v>
-      </c>
-      <c r="I6">
-        <v>-0.3061946902654867</v>
-      </c>
-      <c r="J6">
-        <v>-0.3061946902654867</v>
-      </c>
-      <c r="K6">
-        <v>-3.92</v>
-      </c>
-      <c r="L6">
-        <v>-3.469026548672566</v>
-      </c>
-      <c r="M6">
-        <v>2.4</v>
-      </c>
-      <c r="N6">
-        <v>0.096</v>
-      </c>
-      <c r="O6">
-        <v>-0.6122448979591837</v>
-      </c>
-      <c r="P6">
-        <v>-0</v>
-      </c>
-      <c r="Q6">
-        <v>-0</v>
-      </c>
-      <c r="R6">
-        <v>0</v>
-      </c>
-      <c r="S6">
-        <v>2.4</v>
-      </c>
-      <c r="T6">
-        <v>1</v>
-      </c>
-      <c r="U6">
-        <v>0.874</v>
-      </c>
-      <c r="V6">
-        <v>0.03496</v>
-      </c>
-      <c r="W6">
-        <v>-0.09116279069767441</v>
-      </c>
-      <c r="X6">
-        <v>0.09876909529117857</v>
-      </c>
-      <c r="Y6">
-        <v>-0.189931885988853</v>
-      </c>
-      <c r="Z6">
-        <v>0.1615901615901617</v>
-      </c>
-      <c r="AA6">
-        <v>-0.04947804947804951</v>
-      </c>
-      <c r="AB6">
-        <v>0.08985379054748187</v>
-      </c>
-      <c r="AC6">
-        <v>-0.1393318400255314</v>
-      </c>
-      <c r="AD6">
-        <v>7.17</v>
-      </c>
-      <c r="AE6">
-        <v>0</v>
-      </c>
-      <c r="AF6">
-        <v>7.17</v>
-      </c>
-      <c r="AG6">
-        <v>6.296</v>
-      </c>
-      <c r="AH6">
-        <v>0.222878458190861</v>
-      </c>
-      <c r="AI6">
-        <v>0.1844610239259069</v>
-      </c>
-      <c r="AJ6">
-        <v>0.2011758691206544</v>
-      </c>
-      <c r="AK6">
-        <v>0.1657016528055585</v>
-      </c>
-      <c r="AL6">
-        <v>0.217</v>
-      </c>
-      <c r="AM6">
-        <v>0.092</v>
-      </c>
-      <c r="AN6">
-        <v>-23.9</v>
-      </c>
-      <c r="AO6">
-        <v>-1.594470046082949</v>
-      </c>
-      <c r="AP6">
-        <v>-20.98666666666667</v>
-      </c>
-      <c r="AQ6">
-        <v>-3.760869565217391</v>
+        <v>-2.36094674556213</v>
       </c>
     </row>
   </sheetData>
